--- a/MainTop/06.08.2026 Макс Озон/print_print_sorted.xlsx
+++ b/MainTop/06.08.2026 Макс Озон/print_print_sorted.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\06.08.2026 Макс Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5556C6-7891-4E87-83AB-605E16002E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A55D699-8D2F-4AF2-AE61-DB6D25FC7D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="72">
   <si>
     <t>Артикул</t>
   </si>
@@ -230,6 +230,12 @@
   </si>
   <si>
     <t>6_а4_настройки_60</t>
+  </si>
+  <si>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>Озон на 3 города</t>
   </si>
 </sst>
 </file>
@@ -316,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -325,6 +331,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -627,13 +634,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -655,8 +662,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -678,8 +692,19 @@
       <c r="G2" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="1">
+        <f>G2*5</f>
+        <v>30</v>
+      </c>
+      <c r="I2" s="2">
+        <v>6</v>
+      </c>
+      <c r="J2" s="1">
+        <f>H2+3*I2-D2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -701,8 +726,19 @@
       <c r="G3" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="1">
+        <f t="shared" ref="H3:H59" si="0">G3*5</f>
+        <v>30</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6</v>
+      </c>
+      <c r="J3" s="1">
+        <f t="shared" ref="J3:J59" si="1">H3+3*I3-D3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -724,8 +760,19 @@
       <c r="G4" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I4" s="2">
+        <v>2</v>
+      </c>
+      <c r="J4" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -747,8 +794,19 @@
       <c r="G5" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I5" s="2">
+        <v>2</v>
+      </c>
+      <c r="J5" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -770,8 +828,19 @@
       <c r="G6" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I6" s="2">
+        <v>2</v>
+      </c>
+      <c r="J6" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -793,8 +862,19 @@
       <c r="G7" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I7" s="2">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -816,8 +896,19 @@
       <c r="G8" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I8" s="2">
+        <v>2</v>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -839,8 +930,19 @@
       <c r="G9" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I9" s="2">
+        <v>2</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -862,8 +964,19 @@
       <c r="G10" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H10" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I10" s="2">
+        <v>2</v>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -885,8 +998,19 @@
       <c r="G11" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I11" s="2">
+        <v>2</v>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -908,8 +1032,19 @@
       <c r="G12" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I12" s="2">
+        <v>2</v>
+      </c>
+      <c r="J12" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -931,8 +1066,19 @@
       <c r="G13" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H13" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I13" s="2">
+        <v>2</v>
+      </c>
+      <c r="J13" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -954,8 +1100,19 @@
       <c r="G14" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I14" s="2">
+        <v>2</v>
+      </c>
+      <c r="J14" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -977,8 +1134,19 @@
       <c r="G15" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H15" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I15" s="2">
+        <v>2</v>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -1000,8 +1168,19 @@
       <c r="G16" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I16" s="2">
+        <v>2</v>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -1023,8 +1202,19 @@
       <c r="G17" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H17" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I17" s="2">
+        <v>2</v>
+      </c>
+      <c r="J17" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
@@ -1046,8 +1236,19 @@
       <c r="G18" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I18" s="2">
+        <v>2</v>
+      </c>
+      <c r="J18" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
@@ -1069,8 +1270,19 @@
       <c r="G19" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H19" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I19" s="2">
+        <v>1</v>
+      </c>
+      <c r="J19" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>27</v>
       </c>
@@ -1092,8 +1304,19 @@
       <c r="G20" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H20" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1</v>
+      </c>
+      <c r="J20" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>28</v>
       </c>
@@ -1115,8 +1338,19 @@
       <c r="G21" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H21" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1</v>
+      </c>
+      <c r="J21" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>29</v>
       </c>
@@ -1138,8 +1372,19 @@
       <c r="G22" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H22" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I22" s="3">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>30</v>
       </c>
@@ -1161,8 +1406,19 @@
       <c r="G23" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H23" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I23" s="3">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>31</v>
       </c>
@@ -1184,8 +1440,19 @@
       <c r="G24" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H24" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I24" s="3">
+        <v>1</v>
+      </c>
+      <c r="J24" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>32</v>
       </c>
@@ -1207,8 +1474,19 @@
       <c r="G25" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H25" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I25" s="3">
+        <v>1</v>
+      </c>
+      <c r="J25" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>33</v>
       </c>
@@ -1230,8 +1508,19 @@
       <c r="G26" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H26" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1</v>
+      </c>
+      <c r="J26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>34</v>
       </c>
@@ -1253,8 +1542,19 @@
       <c r="G27" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H27" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1</v>
+      </c>
+      <c r="J27" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>35</v>
       </c>
@@ -1276,8 +1576,19 @@
       <c r="G28" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H28" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I28" s="3">
+        <v>1</v>
+      </c>
+      <c r="J28" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>36</v>
       </c>
@@ -1299,8 +1610,19 @@
       <c r="G29" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H29" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I29" s="3">
+        <v>1</v>
+      </c>
+      <c r="J29" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>37</v>
       </c>
@@ -1322,8 +1644,19 @@
       <c r="G30" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H30" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I30" s="3">
+        <v>1</v>
+      </c>
+      <c r="J30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>38</v>
       </c>
@@ -1345,8 +1678,19 @@
       <c r="G31" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H31" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="I31" s="3">
+        <v>3</v>
+      </c>
+      <c r="J31" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>40</v>
       </c>
@@ -1368,8 +1712,19 @@
       <c r="G32" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H32" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2</v>
+      </c>
+      <c r="J32" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>41</v>
       </c>
@@ -1391,8 +1746,19 @@
       <c r="G33" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H33" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I33" s="3">
+        <v>2</v>
+      </c>
+      <c r="J33" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>42</v>
       </c>
@@ -1414,8 +1780,19 @@
       <c r="G34" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H34" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I34" s="3">
+        <v>2</v>
+      </c>
+      <c r="J34" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>43</v>
       </c>
@@ -1437,8 +1814,19 @@
       <c r="G35" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H35" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I35" s="3">
+        <v>2</v>
+      </c>
+      <c r="J35" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>44</v>
       </c>
@@ -1460,8 +1848,19 @@
       <c r="G36" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H36" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I36" s="3">
+        <v>2</v>
+      </c>
+      <c r="J36" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>45</v>
       </c>
@@ -1483,8 +1882,19 @@
       <c r="G37" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H37" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I37" s="3">
+        <v>2</v>
+      </c>
+      <c r="J37" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>46</v>
       </c>
@@ -1506,8 +1916,19 @@
       <c r="G38" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H38" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I38" s="3">
+        <v>2</v>
+      </c>
+      <c r="J38" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>47</v>
       </c>
@@ -1529,8 +1950,19 @@
       <c r="G39" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H39" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I39" s="3">
+        <v>2</v>
+      </c>
+      <c r="J39" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>48</v>
       </c>
@@ -1552,8 +1984,19 @@
       <c r="G40" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H40" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I40" s="3">
+        <v>2</v>
+      </c>
+      <c r="J40" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>49</v>
       </c>
@@ -1575,8 +2018,19 @@
       <c r="G41" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H41" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I41" s="3">
+        <v>1</v>
+      </c>
+      <c r="J41" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>50</v>
       </c>
@@ -1598,8 +2052,19 @@
       <c r="G42" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H42" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I42" s="3">
+        <v>1</v>
+      </c>
+      <c r="J42" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>51</v>
       </c>
@@ -1621,8 +2086,19 @@
       <c r="G43" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H43" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I43" s="3">
+        <v>1</v>
+      </c>
+      <c r="J43" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>52</v>
       </c>
@@ -1644,8 +2120,19 @@
       <c r="G44" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H44" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I44" s="3">
+        <v>1</v>
+      </c>
+      <c r="J44" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>53</v>
       </c>
@@ -1667,8 +2154,19 @@
       <c r="G45" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H45" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1</v>
+      </c>
+      <c r="J45" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>54</v>
       </c>
@@ -1690,8 +2188,19 @@
       <c r="G46" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H46" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I46" s="3">
+        <v>1</v>
+      </c>
+      <c r="J46" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>55</v>
       </c>
@@ -1713,8 +2222,19 @@
       <c r="G47" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H47" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I47" s="3">
+        <v>1</v>
+      </c>
+      <c r="J47" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>56</v>
       </c>
@@ -1736,8 +2256,19 @@
       <c r="G48" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H48" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I48" s="3">
+        <v>1</v>
+      </c>
+      <c r="J48" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>57</v>
       </c>
@@ -1759,8 +2290,19 @@
       <c r="G49" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H49" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I49" s="3">
+        <v>1</v>
+      </c>
+      <c r="J49" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>58</v>
       </c>
@@ -1782,8 +2324,19 @@
       <c r="G50" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H50" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I50" s="3">
+        <v>1</v>
+      </c>
+      <c r="J50" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>59</v>
       </c>
@@ -1805,8 +2358,19 @@
       <c r="G51" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H51" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I51" s="3">
+        <v>1</v>
+      </c>
+      <c r="J51" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>60</v>
       </c>
@@ -1828,8 +2392,19 @@
       <c r="G52" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H52" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I52" s="4">
+        <v>1</v>
+      </c>
+      <c r="J52" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>61</v>
       </c>
@@ -1851,8 +2426,19 @@
       <c r="G53" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H53" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I53" s="4">
+        <v>1</v>
+      </c>
+      <c r="J53" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>62</v>
       </c>
@@ -1874,8 +2460,19 @@
       <c r="G54" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H54" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I54" s="4">
+        <v>1</v>
+      </c>
+      <c r="J54" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>63</v>
       </c>
@@ -1897,8 +2494,19 @@
       <c r="G55" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H55" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I55" s="4">
+        <v>1</v>
+      </c>
+      <c r="J55" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>64</v>
       </c>
@@ -1920,8 +2528,19 @@
       <c r="G56" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H56" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I56" s="4">
+        <v>1</v>
+      </c>
+      <c r="J56" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>65</v>
       </c>
@@ -1943,8 +2562,19 @@
       <c r="G57" s="5">
         <v>40</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H57" s="1">
+        <f>G57*2</f>
+        <v>80</v>
+      </c>
+      <c r="I57" s="5">
+        <v>80</v>
+      </c>
+      <c r="J57" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>67</v>
       </c>
@@ -1966,8 +2596,18 @@
       <c r="G58" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H58" s="1">
+        <v>26</v>
+      </c>
+      <c r="I58" s="6">
+        <v>18</v>
+      </c>
+      <c r="J58" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>68</v>
       </c>
@@ -1988,6 +2628,17 @@
       </c>
       <c r="G59" s="7">
         <v>1</v>
+      </c>
+      <c r="H59" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I59" s="7">
+        <v>1</v>
+      </c>
+      <c r="J59" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/MainTop/06.08.2026 Макс Озон/print_print_sorted.xlsx
+++ b/MainTop/06.08.2026 Макс Озон/print_print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\06.08.2026 Макс Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A55D699-8D2F-4AF2-AE61-DB6D25FC7D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E0D50C-1AF7-4762-9ABD-7F21F3246FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2563,11 +2563,10 @@
         <v>40</v>
       </c>
       <c r="H57" s="1">
-        <f>G57*2</f>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="I57" s="5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J57" s="1">
         <f t="shared" si="1"/>

--- a/MainTop/06.08.2026 Макс Озон/print_print_sorted.xlsx
+++ b/MainTop/06.08.2026 Макс Озон/print_print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\06.08.2026 Макс Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E0D50C-1AF7-4762-9ABD-7F21F3246FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1247FB77-8005-42AE-86A7-5B55BEB29501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -638,6 +638,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.85546875" customWidth="1"/>
+    <col min="2" max="2" width="4.28515625" customWidth="1"/>
+    <col min="3" max="3" width="4.140625" customWidth="1"/>
+    <col min="4" max="4" width="3.5703125" customWidth="1"/>
+    <col min="5" max="5" width="5.85546875" customWidth="1"/>
+    <col min="10" max="10" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">

--- a/MainTop/06.08.2026 Макс Озон/print_print_sorted.xlsx
+++ b/MainTop/06.08.2026 Макс Озон/print_print_sorted.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\06.08.2026 Макс Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1247FB77-8005-42AE-86A7-5B55BEB29501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D793583-DBBA-4DCA-A68F-971FAB6D5F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -1858,11 +1858,11 @@
         <v>10</v>
       </c>
       <c r="I36" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J36" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
